--- a/data/employees/EMP031/AST-EMP031-06.xlsx
+++ b/data/employees/EMP031/AST-EMP031-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experiment Data Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,184 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Experiment Data Log - Alex Garcia (R&amp;D)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Alex Garcia | Role: Director | Location: Fremont | Date: 2025-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Experiment ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Next Steps</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXP-2026-041</t>
+          <t>EMP031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Low-temp deposition</t>
+          <t>Ast Emp031 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>93</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP disclosure</t>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EXP-2026-042</t>
+          <t>EMP031</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novel etchant blend</t>
+          <t>Ast Emp031 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Section 1: Data quality remediation. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXP-2026-043</t>
+          <t>EMP031</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surface treatment A</t>
+          <t>Ast Emp031 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.51</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Redesign</t>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXP-2026-044</t>
+          <t>EMP031</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plasma optimisation</t>
+          <t>Ast Emp031 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>68</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Start Q3</t>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>64</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>76</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>89</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>72</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>81</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>63</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>99</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>83</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>89</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>81</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>78</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp031 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>67</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP031</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP031 contributes to ast emp031 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>